--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M399"/>
+  <dimension ref="A1:M402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -12348,7 +12348,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>760-290-CM26</t>
+          <t>2446-935-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12368,32 +12368,32 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>11325.3</v>
+        <v>859.83</v>
       </c>
     </row>
     <row r="197">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12470,7 +12470,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2446-935-CM26</t>
+          <t>1091-289-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12495,27 +12495,27 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>76.756.768-5</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>859.83</v>
+        <v>18993.42</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1091-289-CM26</t>
+          <t>760-290-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12551,32 +12551,32 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad Industrial SPA </t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.756.768-5</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>18993.42</v>
+        <v>11325.3</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2735-947-CM26</t>
+          <t>1079659-325-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12617,27 +12617,27 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2034.03</v>
+        <v>1993.22</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>696212-101-CM26</t>
+          <t>607-221-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.809.000-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>PARQUE METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2400.92</v>
+        <v>1752.4</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>607-221-CM26</t>
+          <t>2273-559-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.809.000-0</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>PARQUE METROPOLITANO DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1752.4</v>
+        <v>9581.469999999999</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2273-559-CM26</t>
+          <t>2735-1041-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>9581.469999999999</v>
+        <v>1774.54</v>
       </c>
     </row>
     <row r="204">
@@ -12958,7 +12958,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2735-1041-CM26</t>
+          <t>2735-947-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1774.54</v>
+        <v>2034.03</v>
       </c>
     </row>
     <row r="207">
@@ -13141,7 +13141,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1079659-324-CM26</t>
+          <t>696212-101-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1993.22</v>
+        <v>2400.92</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1079659-325-CM26</t>
+          <t>1079659-324-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13324,7 +13324,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1078078-2985-CM26</t>
+          <t>4491-421-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13349,27 +13349,27 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.150.501-4</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA MERCEL SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.601.843-0</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2056.68</v>
+        <v>1239.3</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1431841-974-CM26</t>
+          <t>3922-752-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13410,27 +13410,27 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>19689.56</v>
+        <v>5210.21</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5040-135-CM26</t>
+          <t>5640-46-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13466,32 +13466,32 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>SOCIEDAD DE INVERSIONES BLUBOX SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>76.616.388-2</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>20916.56</v>
+        <v>26252.75</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1078078-2984-CM26</t>
+          <t>852-233-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13527,32 +13527,32 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>4142.53</v>
+        <v>18091.01</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2111-11642-CM26</t>
+          <t>2111-11649-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>4011.92</v>
+        <v>4432.31</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>4491-421-CM26</t>
+          <t>2111-11645-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13649,32 +13649,32 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.150.501-4</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MERCEL SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>77.601.843-0</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1239.3</v>
+        <v>2721.63</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2111-11649-CM26</t>
+          <t>2111-11642-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4432.31</v>
+        <v>4011.92</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>852-233-CM26</t>
+          <t>1078078-2985-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13771,32 +13771,32 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>18091.01</v>
+        <v>2056.68</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5640-46-CM26</t>
+          <t>1078078-2984-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES BLUBOX SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.616.388-2</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>26252.75</v>
+        <v>4142.53</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3922-752-CM26</t>
+          <t>5040-135-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>5210.21</v>
+        <v>20916.56</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2111-11645-CM26</t>
+          <t>696212-102-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13954,17 +13954,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13989,13 +13989,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2721.63</v>
+        <v>2447.19</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>696212-102-CM26</t>
+          <t>1431841-974-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14020,27 +14020,27 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2447.19</v>
+        <v>19689.56</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5539-138-CM26</t>
+          <t>4081-284-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14076,32 +14076,32 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1489.35</v>
+        <v>1475.35</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4081-284-CM26</t>
+          <t>1126922-1183-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14142,27 +14142,27 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1475.35</v>
+        <v>6379.25</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4371-338-CM26</t>
+          <t>4189-368-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14198,32 +14198,32 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>CROBAK SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.071.404-4</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>7590.96</v>
+        <v>801.76</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1430715-175-CM26</t>
+          <t>2446-819-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14259,17 +14259,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>15395.37</v>
+        <v>35641.79</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2546-795-CM26</t>
+          <t>5153-1376-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14325,27 +14325,27 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>8750.59</v>
+        <v>2546.93</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>759-283-CM26</t>
+          <t>5061-472-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14381,32 +14381,32 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>10404.84</v>
+        <v>7794.57</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5061-472-CM26</t>
+          <t>2446-863-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14442,32 +14442,32 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>7794.57</v>
+        <v>21356.65</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2446-863-CM26</t>
+          <t>2546-795-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14503,32 +14503,32 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14538,13 +14538,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>21356.65</v>
+        <v>8750.59</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5153-1376-CM26</t>
+          <t>5539-138-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2546.93</v>
+        <v>1489.35</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2446-819-CM26</t>
+          <t>1430715-175-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14625,17 +14625,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>35641.79</v>
+        <v>15395.37</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4189-368-CM26</t>
+          <t>4371-338-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14686,32 +14686,32 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>CROBAK SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>77.071.404-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>801.76</v>
+        <v>7590.96</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1126922-1183-CM26</t>
+          <t>759-283-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14747,32 +14747,32 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14782,13 +14782,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>6379.25</v>
+        <v>10404.84</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4734-139-CM26</t>
+          <t>4371-344-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14808,32 +14808,32 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.206.192-9</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2241.93</v>
+        <v>6607.38</v>
       </c>
     </row>
     <row r="237">
@@ -14971,7 +14971,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1134432-588-CM26</t>
+          <t>4734-139-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14991,32 +14991,32 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.265.000-k</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Comercial Disaferco Limitada</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>76.127.832-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15026,13 +15026,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>856.38</v>
+        <v>2241.93</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>4371-344-CM26</t>
+          <t>1134432-588-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15057,27 +15057,27 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
+          <t>Comercial Disaferco Limitada</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.206.192-9</t>
+          <t>76.127.832-0</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15087,13 +15087,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>6607.38</v>
+        <v>856.38</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1432083-2050-CM26</t>
+          <t>4794-92-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15118,27 +15118,27 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>INVERSIONES CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.795.374-5</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15148,13 +15148,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1946.08</v>
+        <v>11052.25</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4794-92-CM26</t>
+          <t>1432083-2050-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15179,27 +15179,27 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.795.374-5</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>11052.25</v>
+        <v>1946.08</v>
       </c>
     </row>
     <row r="243">
@@ -15398,7 +15398,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1232366-97-CM26</t>
+          <t>4451-511-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15423,27 +15423,27 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>960.0599999999999</v>
+        <v>3567.87</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>696212-104-CM26</t>
+          <t>1232366-97-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15514,13 +15514,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1239.63</v>
+        <v>960.0599999999999</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1393093-721-CM26</t>
+          <t>696212-104-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15540,32 +15540,32 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>52564.13</v>
+        <v>1239.63</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3634-367-CM26</t>
+          <t>1393093-721-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15606,27 +15606,27 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15636,13 +15636,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1692.67</v>
+        <v>52564.13</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4451-512-CM26</t>
+          <t>3634-367-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15662,32 +15662,32 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -15697,13 +15697,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2060.61</v>
+        <v>1692.67</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1953-1536-CM26</t>
+          <t>4451-512-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15723,32 +15723,32 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15758,13 +15758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1463.17</v>
+        <v>2060.61</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4451-511-CM26</t>
+          <t>3287-427-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15804,12 +15804,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t xml:space="preserve">Ingeniería eléctrica Ingelor Limitada  </t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.218.691-6</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15819,13 +15819,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3567.87</v>
+        <v>3694.45</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3810-790-CM26</t>
+          <t>1953-1536-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15850,27 +15850,27 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15880,13 +15880,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>3545.6</v>
+        <v>1463.17</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1810-36-CM26</t>
+          <t>3810-790-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15911,27 +15911,27 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -15941,13 +15941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>816.08</v>
+        <v>3545.6</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3810-788-CM26</t>
+          <t>1810-36-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15972,27 +15972,27 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16002,13 +16002,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>5286.19</v>
+        <v>816.08</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1057489-9714-CM26</t>
+          <t>3810-788-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>13513.56</v>
+        <v>5286.19</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2905-558-CM26</t>
+          <t>1057489-9714-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16089,32 +16089,32 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16124,13 +16124,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3114.46</v>
+        <v>13513.56</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2132-257-CM26</t>
+          <t>2905-558-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16150,32 +16150,32 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16185,13 +16185,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>4424.21</v>
+        <v>3114.46</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3287-427-CM26</t>
+          <t>2132-257-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16211,17 +16211,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniería eléctrica Ingelor Limitada  </t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>77.218.691-6</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>3694.45</v>
+        <v>4424.21</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2656-929-CM26</t>
+          <t>656-166-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16267,37 +16267,37 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>69.150.100-0</t>
+          <t>61.818.001-8</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOME</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2694.68</v>
+        <v>795.91</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>552975-510-CM26</t>
+          <t>1078078-3035-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16353,12 +16353,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1476.03</v>
+        <v>2304.91</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1057553-309-CM26</t>
+          <t>2656-929-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16394,32 +16394,32 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>69.150.100-0</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16429,13 +16429,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1240.17</v>
+        <v>2694.68</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>769-600-CM26</t>
+          <t>552975-510-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16460,27 +16460,27 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>69.070.301-7</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16490,13 +16490,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>17586.15</v>
+        <v>1476.03</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2289-749-CM26</t>
+          <t>1057553-309-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16516,32 +16516,32 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16551,13 +16551,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>6078.68</v>
+        <v>1240.17</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1078078-3035-CM26</t>
+          <t>769-600-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16582,27 +16582,27 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2304.91</v>
+        <v>17586.15</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1057543-1402-CM26</t>
+          <t>2289-749-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16643,27 +16643,27 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.607.201-3</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>804.6900000000001</v>
+        <v>6078.68</v>
       </c>
     </row>
     <row r="267">
@@ -16801,7 +16801,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1432083-2078-CM26</t>
+          <t>4660-18-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16826,27 +16826,27 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -16856,13 +16856,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>3061.21</v>
+        <v>1485.45</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2345-408-CM26</t>
+          <t>1432083-2078-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16882,32 +16882,32 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -16917,13 +16917,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>37225.6</v>
+        <v>3061.21</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4358-170-CM26</t>
+          <t>2345-408-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16943,32 +16943,32 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -16978,13 +16978,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1109.45</v>
+        <v>37225.6</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>960860-19-CM26</t>
+          <t>4358-170-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17004,32 +17004,32 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.180.500-K</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17039,13 +17039,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3642.57</v>
+        <v>1109.45</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>750998-103-CM26</t>
+          <t>960860-19-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17070,27 +17070,27 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.255.100-1</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17100,13 +17100,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>16030.11</v>
+        <v>3642.57</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4660-18-CM26</t>
+          <t>750998-103-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>69.255.100-1</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17146,12 +17146,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17161,13 +17161,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1485.45</v>
+        <v>16030.11</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5510-78-CM26</t>
+          <t>1057543-1402-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17182,37 +17182,37 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>SICMER SERVICIOS DE INGENIERÍA, CONSTRUCCIÓN Y MERCADO SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>77.066.574-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>13488.48</v>
+        <v>804.6900000000001</v>
       </c>
     </row>
     <row r="276">
@@ -17411,7 +17411,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2111-11768-CM26</t>
+          <t>2799-855-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17436,27 +17436,27 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.851.313-9</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -17466,13 +17466,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1221.5</v>
+        <v>806.34</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2432-567-CM26</t>
+          <t>1432083-2112-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17492,32 +17492,32 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
@@ -17527,13 +17527,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>21797.12</v>
+        <v>3454.5</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1421874-140-CM26</t>
+          <t>2111-11768-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17558,12 +17558,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>65.081.269-7</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>FUNDACION CENTRO CULTURAL DE LO PRADO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17573,12 +17573,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1148.87</v>
+        <v>1221.5</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>542753-52-CM26</t>
+          <t>4451-521-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17614,32 +17614,32 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>nuevo amanecer</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>52.003.040-9</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2723.91</v>
+        <v>3391.32</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2799-855-CM26</t>
+          <t>1421874-140-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17680,27 +17680,27 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>65.081.269-7</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>FUNDACION CENTRO CULTURAL DE LO PRADO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>806.34</v>
+        <v>1148.87</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1250341-12-CM26</t>
+          <t>5510-78-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17736,32 +17736,32 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SICMER SERVICIOS DE INGENIERÍA, CONSTRUCCIÓN Y MERCADO SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.066.574-4</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17771,13 +17771,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>994.11</v>
+        <v>13488.48</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>4451-521-CM26</t>
+          <t>2432-567-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17802,27 +17802,27 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -17832,13 +17832,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>3391.32</v>
+        <v>21797.12</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2432-563-CM26</t>
+          <t>542753-52-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17858,17 +17858,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17878,12 +17878,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>nuevo amanecer</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>52.003.040-9</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -17893,13 +17893,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>11538.48</v>
+        <v>2723.91</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3477-594-CM26</t>
+          <t>1171085-37-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17919,32 +17919,32 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>EASY RETAIL S.A. .-</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>76.568.660-1</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
@@ -17954,13 +17954,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>17497.44</v>
+        <v>922.79</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>3217-130-CM26</t>
+          <t>2432-564-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17980,32 +17980,32 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Comercial Disaferco Limitada</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>76.127.832-0</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
@@ -18015,13 +18015,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>5991.8</v>
+        <v>3197.29</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1432083-2112-CM26</t>
+          <t>2432-563-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18041,32 +18041,32 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>3454.5</v>
+        <v>11538.48</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2799-847-CM26</t>
+          <t>3477-594-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18102,32 +18102,32 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>EASY RETAIL S.A. .-</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.568.660-1</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>6318.07</v>
+        <v>17497.44</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1801-102-CM26</t>
+          <t>3217-130-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18163,32 +18163,32 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>Comercial Disaferco Limitada</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.127.832-0</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1153.75</v>
+        <v>5991.8</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3712-558-CM26</t>
+          <t>2799-847-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18224,32 +18224,32 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18259,13 +18259,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>6429.61</v>
+        <v>6318.07</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1171085-37-CM26</t>
+          <t>1801-102-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18290,27 +18290,27 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18320,13 +18320,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>922.79</v>
+        <v>1153.75</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>3316-141-CM26</t>
+          <t>3712-558-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18351,27 +18351,27 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18381,13 +18381,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>9230.120000000001</v>
+        <v>6429.61</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2432-564-CM26</t>
+          <t>3316-141-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18407,17 +18407,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18442,13 +18442,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3197.29</v>
+        <v>9230.120000000001</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1002-387-CM26</t>
+          <t>1250341-12-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18463,37 +18463,37 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>26926.91</v>
+        <v>994.11</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3289-116-CM26</t>
+          <t>2324-1155-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18534,12 +18534,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18549,12 +18549,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -18564,13 +18564,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>985.21</v>
+        <v>15005.63</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2432-573-CM26</t>
+          <t>1002-387-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18595,27 +18595,27 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18625,13 +18625,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2729.49</v>
+        <v>26926.91</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2324-1155-CM26</t>
+          <t>3289-116-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18656,12 +18656,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -18686,13 +18686,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>15005.63</v>
+        <v>985.21</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1968-2126-CM26</t>
+          <t>2432-573-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18717,27 +18717,27 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1171.86</v>
+        <v>2729.49</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2279-569-CM26</t>
+          <t>1968-2126-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18778,27 +18778,27 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
@@ -18808,13 +18808,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>8110.2</v>
+        <v>1171.86</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1037-89-CM26</t>
+          <t>1157-347-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18839,27 +18839,27 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -18869,13 +18869,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3780.1</v>
+        <v>2049.17</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1157-347-CM26</t>
+          <t>852-246-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18900,27 +18900,27 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>HELLMUN EDMUNDO ARAVENA ILLESCA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>7.960.498-4</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -18930,13 +18930,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2049.17</v>
+        <v>7123.29</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1079580-324-CM26</t>
+          <t>1037-89-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18961,27 +18961,27 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -18991,13 +18991,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>28309.1</v>
+        <v>3780.1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>852-245-CM26</t>
+          <t>1079580-324-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19017,32 +19017,32 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>HELLMUN EDMUNDO ARAVENA ILLESCA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>7.960.498-4</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -19052,13 +19052,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>8035.66</v>
+        <v>28309.1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>852-246-CM26</t>
+          <t>2279-569-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19083,27 +19083,27 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>HELLMUN EDMUNDO ARAVENA ILLESCA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>7.960.498-4</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -19113,13 +19113,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>7123.29</v>
+        <v>8110.2</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2385-654-CM26</t>
+          <t>852-245-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19139,32 +19139,32 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>HELLMUN EDMUNDO ARAVENA ILLESCA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>7.960.498-4</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19174,13 +19174,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>9560.469999999999</v>
+        <v>8035.66</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>4548-528-CM26</t>
+          <t>2385-654-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19200,32 +19200,32 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19235,13 +19235,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2286.53</v>
+        <v>9560.469999999999</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1432083-2086-CM26</t>
+          <t>4548-528-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19261,32 +19261,32 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>99.590.760-7</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
@@ -19296,13 +19296,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1076.12</v>
+        <v>2286.53</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2111-11780-CM26</t>
+          <t>2731-719-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19322,17 +19322,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19342,12 +19342,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19357,13 +19357,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>4809.64</v>
+        <v>2425.48</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>967-22-CM26</t>
+          <t>2111-11780-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19383,32 +19383,32 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>984.97</v>
+        <v>4809.64</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>5195-161-CM26</t>
+          <t>967-22-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19444,32 +19444,32 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>65.743.680-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
@@ -19479,13 +19479,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3170.21</v>
+        <v>984.97</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5195-163-CM26</t>
+          <t>5195-161-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -19540,13 +19540,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>13118.96</v>
+        <v>3170.21</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2731-719-CM26</t>
+          <t>5195-163-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19566,17 +19566,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>65.743.680-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19586,12 +19586,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -19601,13 +19601,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2425.48</v>
+        <v>13118.96</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1417913-667-CM26</t>
+          <t>1432083-2086-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19627,32 +19627,32 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -19662,13 +19662,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1230.2</v>
+        <v>1076.12</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3223-147-CM26</t>
+          <t>1417913-667-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19688,32 +19688,32 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.102.019-8</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Comercial Disaferco Limitada</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>76.127.832-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -19723,13 +19723,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1533.55</v>
+        <v>1230.2</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2785-595-CM26</t>
+          <t>3223-147-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19749,32 +19749,32 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>61.102.019-8</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>Comercial Disaferco Limitada</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.127.832-0</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -19784,13 +19784,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>8077.95</v>
+        <v>1533.55</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2698-203-CM26</t>
+          <t>2785-595-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19815,27 +19815,27 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K318" t="inlineStr"/>
@@ -19845,13 +19845,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>5408.45</v>
+        <v>8077.95</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>707424-66-CM26</t>
+          <t>2698-203-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19871,32 +19871,32 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K319" t="inlineStr"/>
@@ -19906,13 +19906,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2153.29</v>
+        <v>5408.45</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>4305-119-CM26</t>
+          <t>707424-66-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19937,27 +19937,27 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -19967,13 +19967,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>788.51</v>
+        <v>2153.29</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2699-61-CM26</t>
+          <t>4305-119-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -19993,32 +19993,32 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.070.600-8</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA REINA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -20028,13 +20028,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3665.77</v>
+        <v>788.51</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3709-899-CM26</t>
+          <t>2699-61-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -20059,27 +20059,27 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.070.600-8</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE LA REINA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K322" t="inlineStr"/>
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1539.19</v>
+        <v>3665.77</v>
       </c>
     </row>
     <row r="323">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -20705,7 +20705,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1350767-139-CM26</t>
+          <t>696212-107-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -20725,32 +20725,32 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K333" t="inlineStr"/>
@@ -20760,13 +20760,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>4976.89</v>
+        <v>1108.45</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4597-26-CM26</t>
+          <t>3709-899-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20786,32 +20786,32 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.826.000-3</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K334" t="inlineStr"/>
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>832.09</v>
+        <v>1539.19</v>
       </c>
     </row>
     <row r="335">
@@ -20888,7 +20888,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>4085-554-CM26</t>
+          <t>4597-26-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20913,27 +20913,27 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>61.826.000-3</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K336" t="inlineStr"/>
@@ -20943,13 +20943,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>11086.28</v>
+        <v>832.09</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5517-337-CM26</t>
+          <t>2735-1020-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -20969,17 +20969,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -20989,12 +20989,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COMERCIAL GRACIELA LISETH SUAREZ SUAREZ E.I.R.L.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>76.698.741-9</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K337" t="inlineStr"/>
@@ -21004,13 +21004,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>3588.34</v>
+        <v>1404.17</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2974-259-CM26</t>
+          <t>2735-1022-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21035,12 +21035,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21050,12 +21050,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -21065,13 +21065,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>4345.78</v>
+        <v>5805.38</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3512-741-CM26</t>
+          <t>3712-564-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21091,17 +21091,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21111,12 +21111,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K339" t="inlineStr"/>
@@ -21126,13 +21126,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>6538.5</v>
+        <v>4871.19</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>951405-306-CM26</t>
+          <t>1350767-139-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -21167,17 +21167,17 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K340" t="inlineStr"/>
@@ -21187,13 +21187,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1425.14</v>
+        <v>4976.89</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3712-564-CM26</t>
+          <t>3512-741-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21213,17 +21213,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21233,12 +21233,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K341" t="inlineStr"/>
@@ -21248,13 +21248,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>4871.19</v>
+        <v>6538.5</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2735-1020-CM26</t>
+          <t>2974-259-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21274,17 +21274,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21294,12 +21294,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K342" t="inlineStr"/>
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1404.17</v>
+        <v>4345.78</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>696212-107-CM26</t>
+          <t>5517-337-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21335,17 +21335,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21355,12 +21355,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIAL GRACIELA LISETH SUAREZ SUAREZ E.I.R.L.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.698.741-9</t>
         </is>
       </c>
       <c r="K343" t="inlineStr"/>
@@ -21370,13 +21370,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1108.45</v>
+        <v>3588.34</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1208066-329-CM26</t>
+          <t>4085-554-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -21401,12 +21401,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21416,12 +21416,12 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -21431,13 +21431,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>1192.61</v>
+        <v>11086.28</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1002-392-CM26</t>
+          <t>951405-306-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21452,37 +21452,37 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -21492,13 +21492,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>10508.41</v>
+        <v>1425.14</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2343-476-CM26</t>
+          <t>2785-604-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21523,27 +21523,27 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K346" t="inlineStr"/>
@@ -21553,13 +21553,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2552.4</v>
+        <v>1037.65</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2297-1114-CM26</t>
+          <t>2852-855-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -21584,12 +21584,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21599,12 +21599,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -21614,13 +21614,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>810.38</v>
+        <v>1776.58</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1079580-330-CM26</t>
+          <t>4794-93-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21645,27 +21645,27 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL MODO SPA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.712.337-K</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1193.6</v>
+        <v>7839.55</v>
       </c>
     </row>
     <row r="349">
@@ -21742,7 +21742,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>4794-93-CM26</t>
+          <t>3544-207-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21762,32 +21762,32 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>COMERCIAL MODO SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>76.712.337-K</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K350" t="inlineStr"/>
@@ -21797,13 +21797,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>7839.55</v>
+        <v>4865.42</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2852-855-CM26</t>
+          <t>2297-1114-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -21828,12 +21828,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21843,12 +21843,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>77.084.730-3</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -21858,13 +21858,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1776.58</v>
+        <v>810.38</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>3544-207-CM26</t>
+          <t>1002-392-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21884,32 +21884,32 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K352" t="inlineStr"/>
@@ -21919,13 +21919,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>4865.42</v>
+        <v>10508.41</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2785-604-CM26</t>
+          <t>1208066-329-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -21950,27 +21950,27 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K353" t="inlineStr"/>
@@ -21980,13 +21980,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1037.65</v>
+        <v>1192.61</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>586-395-CM26</t>
+          <t>1079580-330-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22011,27 +22011,27 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K354" t="inlineStr"/>
@@ -22041,13 +22041,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>10708.99</v>
+        <v>1193.6</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>3371-31-CM26</t>
+          <t>2343-476-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22067,32 +22067,32 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.946.700-0</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -22102,13 +22102,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3864.76</v>
+        <v>2552.4</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>3712-568-CM26</t>
+          <t>2785-603-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22128,32 +22128,32 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K356" t="inlineStr"/>
@@ -22163,13 +22163,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>989.41</v>
+        <v>1032.51</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1346282-354-CM26</t>
+          <t>3709-909-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22194,27 +22194,27 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -22224,13 +22224,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>2335.54</v>
+        <v>1527.48</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1375761-1533-CM26</t>
+          <t>3371-31-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22250,32 +22250,32 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>61.946.700-0</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.851.313-9</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -22285,13 +22285,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>7929.25</v>
+        <v>3864.76</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2961-593-CM26</t>
+          <t>3712-568-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22311,32 +22311,32 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>COMERCIAL TREBOL LIMITADA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>77.601.801-5</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -22346,13 +22346,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>7972.09</v>
+        <v>989.41</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1655-286-CM26</t>
+          <t>1346282-354-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22372,22 +22372,22 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22407,13 +22407,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2447.18</v>
+        <v>2335.54</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2713-937-CM26</t>
+          <t>1375761-1533-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -22438,17 +22438,17 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22468,13 +22468,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>813.89</v>
+        <v>7929.25</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>3709-909-CM26</t>
+          <t>2961-593-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -22499,27 +22499,27 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL TREBOL LIMITADA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.601.801-5</t>
         </is>
       </c>
       <c r="K362" t="inlineStr"/>
@@ -22529,13 +22529,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1527.48</v>
+        <v>7972.09</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3316-173-CM26</t>
+          <t>586-395-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -22560,27 +22560,27 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -22590,13 +22590,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>869.35</v>
+        <v>10708.99</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2785-603-CM26</t>
+          <t>1655-286-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22621,17 +22621,17 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>61.608.605-7</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22651,13 +22651,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>1032.51</v>
+        <v>2447.18</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1028871-512-CM26</t>
+          <t>2713-937-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -22672,37 +22672,37 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>76.488.070-6</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K365" t="inlineStr"/>
@@ -22712,13 +22712,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>36484.16</v>
+        <v>813.89</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>3494-292-CM26</t>
+          <t>3316-173-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -22733,7 +22733,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -22743,27 +22743,27 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K366" t="inlineStr"/>
@@ -22773,13 +22773,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>8124.28</v>
+        <v>869.35</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>707425-159-CM26</t>
+          <t>1028871-512-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -22804,27 +22804,27 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
+          <t>76.488.070-6</t>
         </is>
       </c>
       <c r="K367" t="inlineStr"/>
@@ -22834,13 +22834,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>18919.15</v>
+        <v>36484.16</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>691944-114-CM26</t>
+          <t>3494-292-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -22860,32 +22860,32 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>CROBAK SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>77.071.404-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K368" t="inlineStr"/>
@@ -22895,13 +22895,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>19683.33</v>
+        <v>8124.28</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>3172-239-CM26</t>
+          <t>707425-159-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -22926,27 +22926,27 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.856.309-8</t>
         </is>
       </c>
       <c r="K369" t="inlineStr"/>
@@ -22956,13 +22956,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>787.9</v>
+        <v>18919.15</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>3544-213-CM26</t>
+          <t>691944-114-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -22987,27 +22987,27 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>CROBAK SPA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.071.404-4</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -23017,13 +23017,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>32690.15</v>
+        <v>19683.33</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1027-74-CM26</t>
+          <t>3172-239-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23043,32 +23043,32 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K371" t="inlineStr"/>
@@ -23078,13 +23078,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>38028.43</v>
+        <v>787.9</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>3921-434-CM26</t>
+          <t>1027-74-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23109,27 +23109,27 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K372" t="inlineStr"/>
@@ -23139,13 +23139,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>9903.24</v>
+        <v>38028.43</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2487-35-CM26</t>
+          <t>3921-434-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23170,27 +23170,27 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K373" t="inlineStr"/>
@@ -23200,13 +23200,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>17291.24</v>
+        <v>9903.24</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>769-605-CM26</t>
+          <t>707425-156-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23226,32 +23226,32 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.084.730-3</t>
         </is>
       </c>
       <c r="K374" t="inlineStr"/>
@@ -23261,13 +23261,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>3432.37</v>
+        <v>13381.33</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>359-2725-CM26</t>
+          <t>3544-213-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23292,27 +23292,27 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.608.404-6</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Instituto Nacional del Cancer</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -23322,13 +23322,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2457.3</v>
+        <v>32690.15</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2453-653-CM26</t>
+          <t>769-605-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -23348,32 +23348,32 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>SOC FLORENTINO GARCIA Y CIA LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>78.132.370-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K376" t="inlineStr"/>
@@ -23383,13 +23383,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>7626.16</v>
+        <v>3432.37</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1943-313-CM26</t>
+          <t>359-2725-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -23409,32 +23409,32 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.608.404-6</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Instituto Nacional del Cancer</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad Industrial SPA </t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>76.756.768-5</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K377" t="inlineStr"/>
@@ -23444,13 +23444,13 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1736.29</v>
+        <v>2457.3</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>993-199-CM26</t>
+          <t>2453-653-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -23475,27 +23475,27 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOC FLORENTINO GARCIA Y CIA LIMITADA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>78.132.370-5</t>
         </is>
       </c>
       <c r="K378" t="inlineStr"/>
@@ -23505,13 +23505,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1721.37</v>
+        <v>7626.16</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>872535-259-CM26</t>
+          <t>1943-313-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -23536,27 +23536,27 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL A M W S.A.</t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>77.714.930-k</t>
+          <t>76.756.768-5</t>
         </is>
       </c>
       <c r="K379" t="inlineStr"/>
@@ -23566,13 +23566,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>803.2</v>
+        <v>1736.29</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>4351-389-CM26</t>
+          <t>993-199-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -23597,27 +23597,27 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K380" t="inlineStr"/>
@@ -23627,13 +23627,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2259.3</v>
+        <v>1721.37</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>707425-156-CM26</t>
+          <t>872535-259-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -23653,32 +23653,32 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>SOC COMERCIAL A M W S.A.</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
+          <t>77.714.930-k</t>
         </is>
       </c>
       <c r="K381" t="inlineStr"/>
@@ -23688,13 +23688,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>13381.33</v>
+        <v>803.2</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4174-421-CM26</t>
+          <t>4351-389-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -23709,37 +23709,37 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
@@ -23749,13 +23749,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>6838.86</v>
+        <v>2259.3</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1432083-2168-CM26</t>
+          <t>2487-35-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -23770,37 +23770,37 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>99.590.760-7</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -23810,13 +23810,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>4659.87</v>
+        <v>17291.24</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>48-241-CM26</t>
+          <t>1432083-2168-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -23841,27 +23841,27 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>899.8200000000001</v>
+        <v>4659.87</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1704-4789-CM26</t>
+          <t>48-241-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -23902,17 +23902,17 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23932,13 +23932,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>850.1799999999999</v>
+        <v>899.8200000000001</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2171-421-CM26</t>
+          <t>1704-4789-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.606.611-0</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>HOSPITAL SAN AGUSTIN DE LA LIGUA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -23978,12 +23978,12 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K386" t="inlineStr"/>
@@ -23993,13 +23993,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2791.07</v>
+        <v>850.1799999999999</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3755-147-CM26</t>
+          <t>2171-421-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24019,32 +24019,32 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.975.600-2</t>
+          <t>61.606.611-0</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>HOSPITAL SAN AGUSTIN DE LA LIGUA</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K387" t="inlineStr"/>
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>25028.83</v>
+        <v>2791.07</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1415863-18-CM26</t>
+          <t>3755-147-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24085,12 +24085,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.975.600-2</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24100,12 +24100,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K388" t="inlineStr"/>
@@ -24115,13 +24115,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>4245.54</v>
+        <v>25028.83</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2294-1714-CM26</t>
+          <t>1415863-18-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24141,32 +24141,32 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K389" t="inlineStr"/>
@@ -24176,13 +24176,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>776.21</v>
+        <v>4245.54</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2799-876-CM26</t>
+          <t>4174-421-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -24207,27 +24207,27 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
@@ -24237,13 +24237,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2806</v>
+        <v>6838.86</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>3825-270-CM26</t>
+          <t>2294-1714-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -24268,27 +24268,27 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K391" t="inlineStr"/>
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>3215.94</v>
+        <v>776.21</v>
       </c>
     </row>
     <row r="392">
@@ -24365,7 +24365,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1079566-340-CM26</t>
+          <t>1057540-2181-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -24390,27 +24390,27 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALTAS CUMBRES SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>76.959.575-9</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K393" t="inlineStr"/>
@@ -24420,13 +24420,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>26155.87</v>
+        <v>8252.459999999999</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1057544-12596-CM26</t>
+          <t>3825-270-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -24451,27 +24451,27 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K394" t="inlineStr"/>
@@ -24481,13 +24481,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>2087.26</v>
+        <v>3215.94</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2069-7821-CM26</t>
+          <t>1079566-340-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -24507,32 +24507,32 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>SPB SOCIEDAD COMERCIAL SPA</t>
+          <t>SOCIEDAD COMERCIAL ALTAS CUMBRES SPA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>77.743.864-6</t>
+          <t>76.959.575-9</t>
         </is>
       </c>
       <c r="K395" t="inlineStr"/>
@@ -24542,13 +24542,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>3675.61</v>
+        <v>26155.87</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2273-572-CM26</t>
+          <t>1057544-12596-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -24573,27 +24573,27 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K396" t="inlineStr"/>
@@ -24603,13 +24603,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2619.23</v>
+        <v>2087.26</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2273-533-CM26</t>
+          <t>2069-7821-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -24629,17 +24629,17 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -24649,12 +24649,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SPB SOCIEDAD COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.743.864-6</t>
         </is>
       </c>
       <c r="K397" t="inlineStr"/>
@@ -24664,13 +24664,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>806.78</v>
+        <v>3675.61</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2799-868-CM26</t>
+          <t>2273-572-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -24695,27 +24695,27 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K398" t="inlineStr"/>
@@ -24725,13 +24725,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>776.2</v>
+        <v>2619.23</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2436-1155-CM26</t>
+          <t>2273-533-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -24751,32 +24751,32 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K399" t="inlineStr"/>
@@ -24786,6 +24786,189 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
+        <v>806.78</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2799-876-CM26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>69.051.100-2</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>76.851.313-9</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="n">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2799-868-CM26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>69.051.100-2</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="n">
+        <v>776.2</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2436-1155-CM26</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>TECNOQUIM SPA</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>76.378.846-6</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="n">
         <v>11567.68</v>
       </c>
     </row>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1822,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1887,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1952,11 @@
           <t>77.094.046-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2078,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2326,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2391,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2456,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2643,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2830,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2956,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3021,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3147,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3456,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3521,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3830,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3956,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4021,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4208,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4273,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4460,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4525,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4590,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4777,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4842,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4907,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5033,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5159,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5224,11 @@
           <t>76.156.939-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5472,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5903,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5968,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6094,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6159,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6285,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6350,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6415,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6480,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6545,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6976,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7224,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7350,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7476,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7541,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7606,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7854,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7919,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7984,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8293,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8419,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8484,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8915,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8980,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9228,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9354,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9419,11 @@
           <t>77.163.835-K</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9606,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9793,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9919,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9984,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10110,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10236,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10301,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10488,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10553,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10862,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11354,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11602,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11911,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11976,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12041,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12167,11 @@
           <t>77.094.046-K</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12232,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12297,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12423,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12610,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12736,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12923,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12988,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13053,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13179,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13244,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13309,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13374,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13439,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13504,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13569,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13634,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13699,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13764,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13829,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13955,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14020,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14085,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14150,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14459,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14585,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14833,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14898,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15024,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15150,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15215,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15463,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15589,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15715,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15902,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15967,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16032,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16097,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16223,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16349,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16597,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16662,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16727,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16914,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17040,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17105,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17292,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17357,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17483,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17548,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17613,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17678,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17743,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18113,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18422,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18487,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18857,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18922,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19109,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19418,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19666,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +19975,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20406,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20593,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20841,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +20906,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21032,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21158,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21528,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21654,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21719,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21784,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21849,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +21975,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22040,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22166,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22292,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22723,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22788,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +22975,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23040,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23105,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23170,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23296,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23361,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23548,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23613,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +23861,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24048,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24113,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24300,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24548,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24735,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25044,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25170,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25357,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +25666,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
@@ -6033,7 +6033,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10988,7 +10992,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18239,7 +18247,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M402"/>
+  <dimension ref="A1:M405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -12192,7 +12192,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4737-132-CM26</t>
+          <t>760-290-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12212,32 +12212,32 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -12251,7 +12251,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1161.07</v>
+        <v>11325.3</v>
       </c>
     </row>
     <row r="189">
@@ -12883,7 +12883,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>760-290-CM26</t>
+          <t>4737-132-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.685.821-8</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>11325.3</v>
+        <v>1161.07</v>
       </c>
     </row>
     <row r="200">
@@ -13464,7 +13464,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1079659-323-CM26</t>
+          <t>696212-101-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13484,37 +13484,37 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13523,13 +13523,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5979.65</v>
+        <v>2400.92</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>696212-101-CM26</t>
+          <t>1079659-323-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13549,37 +13549,37 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13588,7 +13588,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2400.92</v>
+        <v>5979.65</v>
       </c>
     </row>
     <row r="210">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -19447,7 +19447,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>852-246-CM26</t>
+          <t>2385-654-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19467,32 +19467,32 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>HELLMUN EDMUNDO ARAVENA ILLESCA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>7.960.498-4</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -19502,7 +19502,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>7123.29</v>
+        <v>9560.469999999999</v>
       </c>
     </row>
     <row r="304">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2385-654-CM26</t>
+          <t>852-246-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19781,27 +19781,27 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>HELLMUN EDMUNDO ARAVENA ILLESCA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>7.960.498-4</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19811,7 +19811,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>9560.469999999999</v>
+        <v>7123.29</v>
       </c>
     </row>
     <row r="309">
@@ -19878,7 +19878,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2731-719-CM26</t>
+          <t>1417913-667-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19903,27 +19903,27 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19933,7 +19933,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2425.48</v>
+        <v>1230.2</v>
       </c>
     </row>
     <row r="311">
@@ -20004,7 +20004,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>967-22-CM26</t>
+          <t>3223-147-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20024,32 +20024,32 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.102.019-8</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>Comercial Disaferco Limitada</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>76.127.832-0</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
@@ -20059,13 +20059,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>984.97</v>
+        <v>1533.55</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5195-161-CM26</t>
+          <t>967-22-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20085,32 +20085,32 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>65.743.680-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K313" t="inlineStr"/>
@@ -20120,13 +20120,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>3170.21</v>
+        <v>984.97</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5195-163-CM26</t>
+          <t>5195-161-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20181,7 +20181,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>13118.96</v>
+        <v>3170.21</v>
       </c>
     </row>
     <row r="315">
@@ -20248,7 +20248,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1417913-667-CM26</t>
+          <t>2731-719-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20273,27 +20273,27 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -20303,13 +20303,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1230.2</v>
+        <v>2425.48</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>3223-147-CM26</t>
+          <t>5195-163-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20334,27 +20334,27 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>61.102.019-8</t>
+          <t>65.743.680-1</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Comercial Disaferco Limitada</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>76.127.832-0</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1533.55</v>
+        <v>13118.96</v>
       </c>
     </row>
     <row r="318">
@@ -20683,7 +20683,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2561-314-CM26</t>
+          <t>2713-936-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20708,43 +20708,47 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>61.004.035-7</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>Multinegocios R&amp;G</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>76.494.129-2</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2839.9</v>
+        <v>1330.79</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2341-416-CM26</t>
+          <t>707424-69-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20764,32 +20768,32 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K324" t="inlineStr"/>
@@ -20799,13 +20803,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>16421.06</v>
+        <v>4897.97</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>4455-568-CM26</t>
+          <t>3709-899-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20830,47 +20834,43 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2331.5</v>
+        <v>1539.19</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2790-291-CM26</t>
+          <t>995-55-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20895,47 +20895,43 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1350.99</v>
+        <v>25982.22</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3709-905-CM26</t>
+          <t>3709-904-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20955,7 +20951,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -20990,13 +20986,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1298.69</v>
+        <v>1539.19</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1802-86-CM26</t>
+          <t>2561-314-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21021,47 +21017,43 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.004.035-7</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>Multinegocios R&amp;G</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.494.129-2</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2112.52</v>
+        <v>2839.9</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>3709-904-CM26</t>
+          <t>3709-905-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21116,13 +21108,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1539.19</v>
+        <v>1298.69</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2713-936-CM26</t>
+          <t>2790-291-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21147,17 +21139,17 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -21181,13 +21173,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1330.79</v>
+        <v>1350.99</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>995-55-CM26</t>
+          <t>4455-568-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21207,48 +21199,52 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr"/>
+          <t>77.819.582-8</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>25982.22</v>
+        <v>2331.5</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>707424-69-CM26</t>
+          <t>2341-416-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21268,32 +21264,32 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -21303,13 +21299,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>4897.97</v>
+        <v>16421.06</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>696212-107-CM26</t>
+          <t>1802-86-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21329,48 +21325,52 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1108.45</v>
+        <v>2112.52</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>3709-899-CM26</t>
+          <t>696212-107-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21390,32 +21390,32 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K334" t="inlineStr"/>
@@ -21425,7 +21425,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1539.19</v>
+        <v>1108.45</v>
       </c>
     </row>
     <row r="335">
@@ -21492,7 +21492,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>4597-26-CM26</t>
+          <t>4085-554-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -21517,47 +21517,47 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.826.000-3</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>DAT I GES SPA</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>832.09</v>
+        <v>11086.28</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2735-1020-CM26</t>
+          <t>5517-337-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21577,17 +21577,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21597,28 +21597,32 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIAL GRACIELA LISETH SUAREZ SUAREZ E.I.R.L.</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr"/>
+          <t>76.698.741-9</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1404.17</v>
+        <v>3588.34</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2735-1022-CM26</t>
+          <t>2974-259-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21638,17 +21642,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21658,32 +21662,28 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>5805.38</v>
+        <v>4345.78</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3712-564-CM26</t>
+          <t>3512-741-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21703,17 +21703,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21723,12 +21723,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>4871.19</v>
+        <v>6538.5</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1350767-139-CM26</t>
+          <t>951405-306-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -21783,37 +21783,33 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>4976.89</v>
+        <v>1425.14</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3512-741-CM26</t>
+          <t>3712-564-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21833,17 +21829,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21853,12 +21849,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -21872,13 +21868,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>6538.5</v>
+        <v>4871.19</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2974-259-CM26</t>
+          <t>761391-1035-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21898,12 +21894,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.103.032-0</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -21918,12 +21914,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K342" t="inlineStr"/>
@@ -21933,13 +21929,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>4345.78</v>
+        <v>833.1799999999999</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5517-337-CM26</t>
+          <t>2735-1022-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21964,12 +21960,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21979,12 +21975,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>COMERCIAL GRACIELA LISETH SUAREZ SUAREZ E.I.R.L.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>76.698.741-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -21998,13 +21994,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>3588.34</v>
+        <v>5805.38</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>4085-554-CM26</t>
+          <t>2735-1020-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22024,52 +22020,48 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>11086.28</v>
+        <v>1404.17</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>951405-306-CM26</t>
+          <t>4597-26-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22089,48 +22081,52 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.826.000-3</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1425.14</v>
+        <v>832.09</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2785-604-CM26</t>
+          <t>1350767-139-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22145,37 +22141,37 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -22189,13 +22185,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1037.65</v>
+        <v>4976.89</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2852-855-CM26</t>
+          <t>1079580-330-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22215,32 +22211,32 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -22250,13 +22246,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1776.58</v>
+        <v>1193.6</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4794-93-CM26</t>
+          <t>1208066-329-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22281,47 +22277,43 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>COMERCIAL MODO SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>76.712.337-K</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>7839.55</v>
+        <v>1192.61</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>3085-561-CM26</t>
+          <t>1002-392-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22346,27 +22338,27 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>61.102.023-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -22376,13 +22368,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>2194.74</v>
+        <v>10508.41</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>3544-207-CM26</t>
+          <t>2297-1114-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22402,32 +22394,32 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.084.730-3</t>
         </is>
       </c>
       <c r="K350" t="inlineStr"/>
@@ -22437,13 +22429,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>4865.42</v>
+        <v>810.38</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2297-1114-CM26</t>
+          <t>2343-476-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22463,48 +22455,52 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>810.38</v>
+        <v>2552.4</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1002-392-CM26</t>
+          <t>3085-561-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -22524,32 +22520,32 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.102.023-6</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.750.890-3</t>
         </is>
       </c>
       <c r="K352" t="inlineStr"/>
@@ -22559,13 +22555,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>10508.41</v>
+        <v>2194.74</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1208066-329-CM26</t>
+          <t>4794-93-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22585,48 +22581,52 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL MODO SPA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr"/>
+          <t>76.712.337-K</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1192.61</v>
+        <v>7839.55</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1079580-330-CM26</t>
+          <t>2852-855-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22646,32 +22646,32 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K354" t="inlineStr"/>
@@ -22681,13 +22681,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1193.6</v>
+        <v>1776.58</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2343-476-CM26</t>
+          <t>3544-207-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22707,46 +22707,42 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2552.4</v>
+        <v>4865.42</v>
       </c>
     </row>
     <row r="356">
@@ -22817,7 +22813,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>3709-909-CM26</t>
+          <t>2785-604-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22837,48 +22833,52 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1527.48</v>
+        <v>1037.65</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>3371-31-CM26</t>
+          <t>3709-909-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22903,27 +22903,27 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.946.700-0</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -22933,13 +22933,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>3864.76</v>
+        <v>1527.48</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3712-568-CM26</t>
+          <t>3371-31-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22964,47 +22964,43 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.946.700-0</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.851.313-9</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>989.41</v>
+        <v>3864.76</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1346282-354-CM26</t>
+          <t>3712-568-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23029,12 +23025,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23044,12 +23040,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -23063,13 +23059,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2335.54</v>
+        <v>989.41</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1375761-1533-CM26</t>
+          <t>1346282-354-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23089,37 +23085,37 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -23128,13 +23124,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>7929.25</v>
+        <v>2335.54</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2961-593-CM26</t>
+          <t>1375761-1533-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23154,37 +23150,37 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>COMERCIAL TREBOL LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>77.601.801-5</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -23193,13 +23189,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>7972.09</v>
+        <v>7929.25</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>586-395-CM26</t>
+          <t>2961-593-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23224,43 +23220,47 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL TREBOL LIMITADA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr"/>
+          <t>77.601.801-5</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>10708.99</v>
+        <v>7972.09</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1655-286-CM26</t>
+          <t>586-395-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23280,52 +23280,48 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2447.18</v>
+        <v>10708.99</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2713-937-CM26</t>
+          <t>1655-286-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23350,32 +23346,32 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.608.605-7</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -23384,13 +23380,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>813.89</v>
+        <v>2447.18</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>3316-173-CM26</t>
+          <t>2713-937-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23415,43 +23411,47 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>869.35</v>
+        <v>813.89</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1028871-512-CM26</t>
+          <t>3316-173-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -23476,27 +23476,27 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>76.488.070-6</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K367" t="inlineStr"/>
@@ -23506,13 +23506,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>36484.16</v>
+        <v>869.35</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>3494-292-CM26</t>
+          <t>1028871-512-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -23537,47 +23537,43 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.488.070-6</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>8124.28</v>
+        <v>36484.16</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>707425-159-CM26</t>
+          <t>3494-292-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -23602,27 +23598,27 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
@@ -23636,13 +23632,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>18919.15</v>
+        <v>8124.28</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>691944-114-CM26</t>
+          <t>707425-159-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -23662,48 +23658,52 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>CROBAK SPA</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>77.071.404-4</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr"/>
+          <t>76.856.309-8</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>19683.33</v>
+        <v>18919.15</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>3172-239-CM26</t>
+          <t>691944-114-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23723,32 +23723,32 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>CROBAK SPA</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.071.404-4</t>
         </is>
       </c>
       <c r="K371" t="inlineStr"/>
@@ -23758,13 +23758,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>787.9</v>
+        <v>19683.33</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1027-74-CM26</t>
+          <t>3172-239-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23784,32 +23784,32 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K372" t="inlineStr"/>
@@ -23819,13 +23819,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>38028.43</v>
+        <v>787.9</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>3921-434-CM26</t>
+          <t>1027-74-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23850,47 +23850,43 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>9903.24</v>
+        <v>38028.43</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>707425-156-CM26</t>
+          <t>3921-434-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23910,48 +23906,52 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
-        </is>
-      </c>
-      <c r="K374" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>13381.33</v>
+        <v>9903.24</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>3544-213-CM26</t>
+          <t>707425-156-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23976,27 +23976,27 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.084.730-3</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -24006,13 +24006,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>32690.15</v>
+        <v>13381.33</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>769-605-CM26</t>
+          <t>3544-213-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24032,52 +24032,48 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K376" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>3432.37</v>
+        <v>32690.15</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>359-2725-CM26</t>
+          <t>769-605-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24097,52 +24093,52 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.608.404-6</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Instituto Nacional del Cancer</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>DAT I GES SPA</t>
-        </is>
-      </c>
-      <c r="J377" t="inlineStr">
-        <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K377" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2457.3</v>
+        <v>3432.37</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2453-653-CM26</t>
+          <t>359-2725-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24167,12 +24163,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>61.608.404-6</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>Instituto Nacional del Cancer</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -24182,28 +24178,32 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>SOC FLORENTINO GARCIA Y CIA LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>78.132.370-5</t>
-        </is>
-      </c>
-      <c r="K378" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>7626.16</v>
+        <v>2457.3</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1943-313-CM26</t>
+          <t>2453-653-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24228,27 +24228,27 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad Industrial SPA </t>
+          <t>SOC FLORENTINO GARCIA Y CIA LIMITADA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>76.756.768-5</t>
+          <t>78.132.370-5</t>
         </is>
       </c>
       <c r="K379" t="inlineStr"/>
@@ -24258,13 +24258,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1736.29</v>
+        <v>7626.16</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>993-199-CM26</t>
+          <t>1943-313-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -24284,52 +24284,48 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K380" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.756.768-5</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>1721.37</v>
+        <v>1736.29</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>872535-259-CM26</t>
+          <t>993-199-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24349,48 +24345,52 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL A M W S.A.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>77.714.930-k</t>
-        </is>
-      </c>
-      <c r="K381" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>803.2</v>
+        <v>1721.37</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4351-389-CM26</t>
+          <t>872535-261-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -24415,27 +24415,27 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
@@ -24445,13 +24445,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>2259.3</v>
+        <v>3606.72</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2487-35-CM26</t>
+          <t>872535-259-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -24471,32 +24471,32 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>SOC COMERCIAL A M W S.A.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>77.714.930-k</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -24506,13 +24506,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>17291.24</v>
+        <v>803.2</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1432083-2168-CM26</t>
+          <t>4351-389-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -24527,57 +24527,53 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>4659.87</v>
+        <v>2259.3</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>48-241-CM26</t>
+          <t>2487-35-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -24592,37 +24588,37 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>99.590.760-7</t>
         </is>
       </c>
       <c r="K385" t="inlineStr"/>
@@ -24632,13 +24628,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>899.8200000000001</v>
+        <v>17291.24</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1704-4789-CM26</t>
+          <t>4174-421-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -24663,27 +24659,27 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K386" t="inlineStr"/>
@@ -24693,13 +24689,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>850.1799999999999</v>
+        <v>6838.86</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2171-421-CM26</t>
+          <t>1415863-18-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24719,46 +24715,42 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.606.611-0</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>HOSPITAL SAN AGUSTIN DE LA LIGUA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2791.07</v>
+        <v>4245.54</v>
       </c>
     </row>
     <row r="388">
@@ -24825,7 +24817,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1415863-18-CM26</t>
+          <t>1432083-2168-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24845,48 +24837,52 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K389" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>4245.54</v>
+        <v>4659.87</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>4174-421-CM26</t>
+          <t>1704-4789-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -24911,27 +24907,27 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
@@ -24941,13 +24937,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>6838.86</v>
+        <v>850.1799999999999</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2294-1714-CM26</t>
+          <t>48-241-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -24972,27 +24968,27 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K391" t="inlineStr"/>
@@ -25002,13 +24998,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>776.21</v>
+        <v>899.8200000000001</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2292-7014-CM26</t>
+          <t>2294-1714-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25028,7 +25024,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -25048,32 +25044,28 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>7586.37</v>
+        <v>776.21</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1057540-2181-CM26</t>
+          <t>2171-421-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25093,48 +25085,52 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.606.611-0</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>HOSPITAL SAN AGUSTIN DE LA LIGUA</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>BROKER SPA</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>77.819.582-8</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
           <t>Biobío</t>
         </is>
       </c>
-      <c r="I393" t="inlineStr">
-        <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
-        </is>
-      </c>
-      <c r="J393" t="inlineStr">
-        <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>8252.459999999999</v>
+        <v>2791.07</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>3825-270-CM26</t>
+          <t>2799-868-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25159,41 +25155,37 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K394" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3215.94</v>
+        <v>776.2</v>
       </c>
     </row>
     <row r="395">
@@ -25260,7 +25252,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1057544-12596-CM26</t>
+          <t>3825-270-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25285,43 +25277,47 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
-        </is>
-      </c>
-      <c r="K396" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2087.26</v>
+        <v>3215.94</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2069-7821-CM26</t>
+          <t>2292-7014-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25346,47 +25342,47 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>SPB SOCIEDAD COMERCIAL SPA</t>
-        </is>
-      </c>
-      <c r="J397" t="inlineStr">
-        <is>
-          <t>77.743.864-6</t>
-        </is>
-      </c>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>3675.61</v>
+        <v>7586.37</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2273-572-CM26</t>
+          <t>1057544-12596-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -25411,27 +25407,27 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K398" t="inlineStr"/>
@@ -25441,13 +25437,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2619.23</v>
+        <v>2087.26</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2273-533-CM26</t>
+          <t>1057544-12595-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -25472,27 +25468,27 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K399" t="inlineStr"/>
@@ -25502,13 +25498,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>806.78</v>
+        <v>1564.35</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2799-876-CM26</t>
+          <t>2069-7821-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25528,48 +25524,52 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>SPB SOCIEDAD COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
-        </is>
-      </c>
-      <c r="K400" t="inlineStr"/>
+          <t>77.743.864-6</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2806</v>
+        <v>3675.61</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2799-868-CM26</t>
+          <t>2273-572-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -25594,27 +25594,27 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K401" t="inlineStr"/>
@@ -25624,71 +25624,254 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>776.2</v>
+        <v>2619.23</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
+          <t>2273-533-CM26</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>69.253.800-5</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="n">
+        <v>806.78</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2799-876-CM26</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>69.051.100-2</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>76.851.313-9</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="n">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>1057540-2181-CM26</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>61.602.198-2</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="n">
+        <v>8252.459999999999</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
           <t>2436-1155-CM26</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>2239-9-LR23</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr">
+      <c r="E405" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
+      <c r="F405" t="inlineStr">
         <is>
           <t>69.100.100-8</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
+      <c r="G405" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
+      <c r="H405" t="inlineStr">
         <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr">
+      <c r="I405" t="inlineStr">
         <is>
           <t>TECNOQUIM SPA</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr">
+      <c r="J405" t="inlineStr">
         <is>
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr">
+      <c r="K405" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M402" s="2" t="n">
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="n">
         <v>11567.68</v>
       </c>
     </row>
